--- a/docs/invoice_for_payment.xlsx
+++ b/docs/invoice_for_payment.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10912"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Amin\Desktop\Arenda_Gira\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shamilsadykov/Desktop/Gira_MAX/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB7924F9-AE4B-4EBE-B83B-17C99A428A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBD1A81D-0BAC-F447-9534-9E674DF4BE9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="1060" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
@@ -24,243 +24,202 @@
   <si>
     <r>
       <rPr>
-        <sz val="9"/>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ПАО "АК БАРС" БАНК
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
+      <t>ПАО "АК БАРС" БАНК
+Банк получателя</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t>Банк получателя</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>БИК</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t>БИК</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>Сч. №</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t>Сч. №</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>30101810000000000805</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t>30101810000000000805</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>ИНН    1655447120</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t>ИНН    1655447120</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>КПП     165501001</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t>КПП     165501001</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>40702810300020016438</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t>40702810300020016438</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>ООО "ГИРА"
+Получатель</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">ООО "ГИРА"
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
+      <t xml:space="preserve">Поставщик:   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ООО "ГИРА", ИНН 1655447120, КПП 165501001, Россия, 420097, Татарстан Респ, г Казань, ул Достоевского, д 74А, кв 1003</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>№</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Товар</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Кол-во</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ед.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Цена</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Сумма</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t>Получатель</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
+      <t>10[3*] усл.
+ед</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Общая сумма по счету:
+Без НДС</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="Microsoft Sans Serif"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Поставщик:   </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>ООО "ГИРА", ИНН 1655447120, КПП 165501001, Россия, 420097, Татарстан Респ, г Казань, ул Достоевского, д 74А, кв 1003</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>№</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Товар</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Кол-во</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ед.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Цена</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Сумма</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Microsoft Sans Serif"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">10[3*] усл.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Microsoft Sans Serif"/>
-        <family val="2"/>
-      </rPr>
-      <t>ед</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Общая сумма по счету:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Без НДС</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="7"/>
-        <rFont val="Microsoft Sans Serif"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(сумма прописью)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Microsoft Sans Serif"/>
-        <family val="2"/>
-      </rPr>
-      <t>Дополнительная информация</t>
+      <t>(сумма прописью)
+Дополнительная информация</t>
     </r>
   </si>
 </sst>
@@ -271,49 +230,11 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="000000000"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Microsoft Sans Serif"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft Sans Serif"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft Sans Serif"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Microsoft Sans Serif"/>
-      <family val="2"/>
       <charset val="204"/>
     </font>
     <font>
@@ -324,43 +245,58 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="16"/>
       <name val="Microsoft Sans Serif"/>
       <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="22"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="7"/>
-      <name val="Microsoft Sans Serif"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="16"/>
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="204"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
+      <b/>
+      <sz val="16"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -482,7 +418,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -495,13 +431,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -510,22 +446,22 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="8" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="3"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="3"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -534,10 +470,10 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -546,10 +482,10 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -558,112 +494,103 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="8" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="3"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="4"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -738,9 +665,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
+      <xdr:colOff>19050</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="7048500" cy="0"/>
     <xdr:sp macro="" textlink="">
@@ -756,7 +683,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
+          <a:off x="19050" y="5930900"/>
           <a:ext cx="7048500" cy="0"/>
         </a:xfrm>
         <a:custGeom>
@@ -785,6 +712,50 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>215900</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>647701</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1206500</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>747201</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Рисунок 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31D0742E-5FCA-7A41-BA16-BF9E484438EF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8369300" y="5505451"/>
+          <a:ext cx="1397000" cy="1575875"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1113,118 +1084,118 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="2" width="5.83203125" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="65.83203125" customWidth="1"/>
-    <col min="5" max="5" width="3.33203125" customWidth="1"/>
+    <col min="1" max="2" width="5.796875" customWidth="1"/>
+    <col min="3" max="3" width="23.3984375" customWidth="1"/>
+    <col min="4" max="4" width="65.796875" customWidth="1"/>
+    <col min="5" max="5" width="3.3984375" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="3.33203125" customWidth="1"/>
-    <col min="8" max="8" width="6.83203125" customWidth="1"/>
-    <col min="9" max="9" width="4.6640625" customWidth="1"/>
-    <col min="10" max="10" width="18.6640625" customWidth="1"/>
-    <col min="11" max="11" width="4.6640625" customWidth="1"/>
-    <col min="12" max="12" width="24.5" customWidth="1"/>
-    <col min="13" max="13" width="4.6640625" customWidth="1"/>
+    <col min="7" max="7" width="3.3984375" customWidth="1"/>
+    <col min="8" max="8" width="15.796875" customWidth="1"/>
+    <col min="9" max="9" width="6.3984375" customWidth="1"/>
+    <col min="10" max="10" width="18.59765625" customWidth="1"/>
+    <col min="11" max="11" width="4.59765625" customWidth="1"/>
+    <col min="12" max="12" width="18.59765625" customWidth="1"/>
+    <col min="13" max="13" width="4.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="54" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="56">
+      <c r="I1" s="52"/>
+      <c r="J1" s="53">
         <v>49205805</v>
       </c>
-      <c r="K1" s="57"/>
-      <c r="L1" s="58"/>
+      <c r="K1" s="54"/>
+      <c r="L1" s="55"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="59" t="s">
+    <row r="2" spans="1:13" ht="39" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="60"/>
-      <c r="J2" s="32" t="s">
+      <c r="I2" s="57"/>
+      <c r="J2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="33"/>
-      <c r="L2" s="34"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="18"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="32" t="s">
+    <row r="3" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="32" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="35" t="s">
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="36"/>
-      <c r="J3" s="39" t="s">
+      <c r="I3" s="33"/>
+      <c r="J3" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="40"/>
-      <c r="L3" s="41"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="38"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="50.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
+    <row r="4" spans="1:13" ht="50.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="47"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="38"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="44"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="43"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="40"/>
+      <c r="L4" s="41"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:13" ht="57.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="58" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="25"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="26"/>
-      <c r="M5" s="26"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+      <c r="J5" s="25"/>
+      <c r="K5" s="25"/>
+      <c r="L5" s="25"/>
+      <c r="M5" s="25"/>
     </row>
-    <row r="6" spans="1:13" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10" t="s">
         <v>8</v>
       </c>
@@ -1241,49 +1212,49 @@
       <c r="L6" s="10"/>
       <c r="M6" s="10"/>
     </row>
-    <row r="7" spans="1:13" ht="35.450000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="27"/>
-      <c r="B7" s="27"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
+    <row r="7" spans="1:13" ht="35.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="26"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="26"/>
+      <c r="L7" s="26"/>
+      <c r="M7" s="26"/>
     </row>
-    <row r="8" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="28" t="s">
+      <c r="B8" s="28"/>
+      <c r="C8" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="30" t="s">
+      <c r="D8" s="28"/>
+      <c r="E8" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="30" t="s">
+      <c r="F8" s="30"/>
+      <c r="G8" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="H8" s="31"/>
-      <c r="I8" s="28" t="s">
+      <c r="H8" s="30"/>
+      <c r="I8" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="28" t="s">
+      <c r="J8" s="28"/>
+      <c r="K8" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="29"/>
+      <c r="L8" s="28"/>
       <c r="M8" s="2"/>
     </row>
-    <row r="9" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="53" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="15">
         <v>1</v>
       </c>
@@ -1304,7 +1275,7 @@
       <c r="L9" s="8"/>
       <c r="M9" s="2"/>
     </row>
-    <row r="10" spans="1:13" ht="42.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="42.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="9"/>
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
@@ -1319,7 +1290,7 @@
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
     </row>
-    <row r="11" spans="1:13" ht="42.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="43" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1351,9 +1322,9 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
     </row>
-    <row r="13" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="4"/>
+    <row r="13" spans="1:13" ht="35" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -1366,7 +1337,7 @@
       <c r="L13" s="5"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13" ht="34.35" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="52" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
         <v>17</v>
       </c>
